--- a/Selenium reports/Selenium_report.xlsx
+++ b/Selenium reports/Selenium_report.xlsx
@@ -4408,7 +4408,7 @@
     <t>PDD-FOOD WEB APPLICATION - TEST SUITE EXECUTIVE SUMMARY</t>
   </si>
   <si>
-    <t>Target URL: https://pdd-food-new.vercel.app  |  User: bunny.akki21@gmail.com  |  Executed: 8/9/2026, 9:58:41 PM  |  Engine: Headless Chrome Selenium Driver</t>
+    <t>Target URL: https://pdd-food-new.vercel.app  |  User: bunny.akki21@gmail.com  |  Executed: 8/9/2026, 10:25:00 PM  |  Engine: Headless Chrome Selenium Driver</t>
   </si>
   <si>
     <t>Total Test Cases</t>

--- a/Selenium reports/Selenium_report.xlsx
+++ b/Selenium reports/Selenium_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2787" uniqueCount="1551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2787" uniqueCount="1557">
   <si>
     <t>PDD-FOOD WEB APPLICATION - COMPLETE END-TO-END TEST CASES REPOSITORY (325 UNIQUE ROWS)</t>
   </si>
@@ -691,7 +691,7 @@
     <t>Click 'Post Food' primary button link in header menu</t>
   </si>
   <si>
-    <t>Navigates to /post-food form page.</t>
+    <t>Navigates to header route /post-food form page.</t>
   </si>
   <si>
     <t>TC050</t>
@@ -703,7 +703,7 @@
     <t>Click 'NGOs &amp; Partners' navigation link in header menu</t>
   </si>
   <si>
-    <t>Navigates to /ngos directory page.</t>
+    <t>Navigates to header route /ngos directory page.</t>
   </si>
   <si>
     <t>TC051</t>
@@ -715,7 +715,7 @@
     <t>Click 'Expired Listings' navigation link in header menu</t>
   </si>
   <si>
-    <t>Navigates to /expired feed page.</t>
+    <t>Navigates to header route /expired feed page.</t>
   </si>
   <si>
     <t>TC052</t>
@@ -1837,7 +1837,7 @@
     <t>Click 'View Details' secondary button on Food Card</t>
   </si>
   <si>
-    <t>Navigates to Food Detail view.</t>
+    <t>Opens dedicated detail view for the clicked food listing.</t>
   </si>
   <si>
     <t>TC136</t>
@@ -2023,7 +2023,7 @@
     <t>Click 3-dots menu on card -&gt; Click 'Report Listing'</t>
   </si>
   <si>
-    <t>Opens report submission modal.</t>
+    <t>Opens quick card action report submission modal.</t>
   </si>
   <si>
     <t>TC150</t>
@@ -2038,7 +2038,7 @@
     <t>Select 'Expired or Spoiled Food' reason in Report modal</t>
   </si>
   <si>
-    <t>Radio option is selected.</t>
+    <t>Expired or spoiled food radio option becomes selected.</t>
   </si>
   <si>
     <t>TC151</t>
@@ -2050,6 +2050,9 @@
     <t>Select 'Incorrect Location Address' reason</t>
   </si>
   <si>
+    <t>Incorrect location address radio option becomes selected.</t>
+  </si>
+  <si>
     <t>TC152</t>
   </si>
   <si>
@@ -2185,6 +2188,9 @@
     <t>Press Enter key while card is focused</t>
   </si>
   <si>
+    <t>Triggers keyboard navigation to Food Detail view.</t>
+  </si>
+  <si>
     <t>TC162</t>
   </si>
   <si>
@@ -2722,6 +2728,9 @@
     <t>Click 'Report Item' link at bottom of detail page</t>
   </si>
   <si>
+    <t>Opens detail view item report submission modal.</t>
+  </si>
+  <si>
     <t>TC201</t>
   </si>
   <si>
@@ -3061,6 +3070,9 @@
     <t>Click 'Post Food' in header navigation bar</t>
   </si>
   <si>
+    <t>Directs browser URL to the /post-food donation creation form.</t>
+  </si>
+  <si>
     <t>TC227</t>
   </si>
   <si>
@@ -3934,6 +3946,9 @@
     <t>Click 'NGOs &amp; Partners' in header navigation bar</t>
   </si>
   <si>
+    <t>Directs browser URL to the /ngos verified partners directory.</t>
+  </si>
+  <si>
     <t>TC292</t>
   </si>
   <si>
@@ -4066,6 +4081,9 @@
     <t>Click 'Expired Listings' in header navigation bar</t>
   </si>
   <si>
+    <t>Directs browser URL to the /expired historical listings feed.</t>
+  </si>
+  <si>
     <t>TC302</t>
   </si>
   <si>
@@ -4408,7 +4426,7 @@
     <t>PDD-FOOD WEB APPLICATION - TEST SUITE EXECUTIVE SUMMARY</t>
   </si>
   <si>
-    <t>Target URL: https://pdd-food-new.vercel.app  |  User: bunny.akki21@gmail.com  |  Executed: 8/9/2026, 10:25:00 PM  |  Engine: Headless Chrome Selenium Driver</t>
+    <t>Target URL: https://pdd-food-new.vercel.app  |  User: bunny.akki21@gmail.com  |  Executed: 8/12/2026, 10:42:51 AM  |  Engine: Headless Chrome Selenium Driver</t>
   </si>
   <si>
     <t>Total Test Cases</t>
@@ -9261,7 +9279,7 @@
         <v>677</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="G155" s="6" t="s">
         <v>16</v>
@@ -9272,7 +9290,7 @@
     </row>
     <row r="156" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="8" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B156" s="9" t="s">
         <v>561</v>
@@ -9281,13 +9299,13 @@
         <v>671</v>
       </c>
       <c r="D156" s="9" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E156" s="9" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F156" s="9" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G156" s="10" t="s">
         <v>16</v>
@@ -9298,22 +9316,22 @@
     </row>
     <row r="157" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B157" s="5" t="s">
         <v>561</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G157" s="6" t="s">
         <v>16</v>
@@ -9324,22 +9342,22 @@
     </row>
     <row r="158" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="8" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B158" s="9" t="s">
         <v>561</v>
       </c>
       <c r="C158" s="9" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D158" s="9" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E158" s="9" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="F158" s="9" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G158" s="10" t="s">
         <v>16</v>
@@ -9350,22 +9368,22 @@
     </row>
     <row r="159" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>561</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G159" s="6" t="s">
         <v>16</v>
@@ -9376,22 +9394,22 @@
     </row>
     <row r="160" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="8" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B160" s="9" t="s">
         <v>561</v>
       </c>
       <c r="C160" s="9" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D160" s="9" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E160" s="9" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F160" s="9" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="G160" s="10" t="s">
         <v>16</v>
@@ -9402,22 +9420,22 @@
     </row>
     <row r="161" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B161" s="5" t="s">
         <v>561</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="G161" s="6" t="s">
         <v>16</v>
@@ -9428,22 +9446,22 @@
     </row>
     <row r="162" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="8" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B162" s="9" t="s">
         <v>561</v>
       </c>
       <c r="C162" s="9" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D162" s="9" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E162" s="9" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="F162" s="9" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="G162" s="10" t="s">
         <v>16</v>
@@ -9454,22 +9472,22 @@
     </row>
     <row r="163" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>561</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="G163" s="6" t="s">
         <v>16</v>
@@ -9480,22 +9498,22 @@
     </row>
     <row r="164" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="8" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B164" s="9" t="s">
         <v>561</v>
       </c>
       <c r="C164" s="9" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D164" s="9" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E164" s="9" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="F164" s="9" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="G164" s="10" t="s">
         <v>16</v>
@@ -9506,22 +9524,22 @@
     </row>
     <row r="165" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>561</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>607</v>
+        <v>724</v>
       </c>
       <c r="G165" s="6" t="s">
         <v>16</v>
@@ -9532,22 +9550,22 @@
     </row>
     <row r="166" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="8" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B166" s="9" t="s">
         <v>561</v>
       </c>
       <c r="C166" s="9" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="D166" s="9" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="E166" s="9" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="F166" s="9" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="G166" s="10" t="s">
         <v>16</v>
@@ -9558,22 +9576,22 @@
     </row>
     <row r="167" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>561</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="G167" s="6" t="s">
         <v>16</v>
@@ -9584,22 +9602,22 @@
     </row>
     <row r="168" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="8" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B168" s="9" t="s">
         <v>561</v>
       </c>
       <c r="C168" s="9" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="D168" s="9" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="E168" s="9" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="F168" s="9" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="G168" s="10" t="s">
         <v>16</v>
@@ -9610,22 +9628,22 @@
     </row>
     <row r="169" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B169" s="5" t="s">
         <v>561</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="G169" s="6" t="s">
         <v>16</v>
@@ -9636,22 +9654,22 @@
     </row>
     <row r="170" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B170" s="9" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C170" s="9" t="s">
         <v>209</v>
       </c>
       <c r="D170" s="9" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="E170" s="9" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="F170" s="9" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="G170" s="10" t="s">
         <v>16</v>
@@ -9662,22 +9680,22 @@
     </row>
     <row r="171" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="G171" s="6" t="s">
         <v>16</v>
@@ -9688,22 +9706,22 @@
     </row>
     <row r="172" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="8" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B172" s="9" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C172" s="9" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D172" s="9" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E172" s="9" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="F172" s="9" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="G172" s="10" t="s">
         <v>16</v>
@@ -9714,22 +9732,22 @@
     </row>
     <row r="173" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="G173" s="6" t="s">
         <v>16</v>
@@ -9740,22 +9758,22 @@
     </row>
     <row r="174" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="8" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B174" s="9" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D174" s="9" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="E174" s="9" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="F174" s="9" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="G174" s="10" t="s">
         <v>16</v>
@@ -9766,22 +9784,22 @@
     </row>
     <row r="175" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="G175" s="6" t="s">
         <v>16</v>
@@ -9792,22 +9810,22 @@
     </row>
     <row r="176" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="8" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B176" s="9" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C176" s="9" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D176" s="9" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="E176" s="9" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="F176" s="9" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="G176" s="10" t="s">
         <v>16</v>
@@ -9818,22 +9836,22 @@
     </row>
     <row r="177" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="G177" s="6" t="s">
         <v>16</v>
@@ -9844,22 +9862,22 @@
     </row>
     <row r="178" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="8" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B178" s="9" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C178" s="9" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D178" s="9" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="E178" s="9" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="F178" s="9" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="G178" s="10" t="s">
         <v>16</v>
@@ -9870,22 +9888,22 @@
     </row>
     <row r="179" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="G179" s="6" t="s">
         <v>16</v>
@@ -9896,22 +9914,22 @@
     </row>
     <row r="180" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="8" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B180" s="9" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C180" s="9" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="D180" s="9" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="E180" s="9" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F180" s="9" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="G180" s="10" t="s">
         <v>16</v>
@@ -9922,22 +9940,22 @@
     </row>
     <row r="181" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="G181" s="6" t="s">
         <v>16</v>
@@ -9948,22 +9966,22 @@
     </row>
     <row r="182" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="8" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B182" s="9" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C182" s="9" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D182" s="9" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="E182" s="9" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="F182" s="9" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="G182" s="10" t="s">
         <v>16</v>
@@ -9974,22 +9992,22 @@
     </row>
     <row r="183" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="G183" s="6" t="s">
         <v>16</v>
@@ -10000,22 +10018,22 @@
     </row>
     <row r="184" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="8" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B184" s="9" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C184" s="9" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D184" s="9" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="E184" s="9" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="F184" s="9" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="G184" s="10" t="s">
         <v>16</v>
@@ -10026,22 +10044,22 @@
     </row>
     <row r="185" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="G185" s="6" t="s">
         <v>16</v>
@@ -10052,22 +10070,22 @@
     </row>
     <row r="186" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="8" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B186" s="9" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C186" s="9" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D186" s="9" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="E186" s="9" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="F186" s="9" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="G186" s="10" t="s">
         <v>16</v>
@@ -10078,22 +10096,22 @@
     </row>
     <row r="187" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="G187" s="6" t="s">
         <v>16</v>
@@ -10104,22 +10122,22 @@
     </row>
     <row r="188" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="8" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B188" s="9" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C188" s="9" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="D188" s="9" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="E188" s="9" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="F188" s="9" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="G188" s="10" t="s">
         <v>16</v>
@@ -10130,22 +10148,22 @@
     </row>
     <row r="189" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="G189" s="11" t="s">
         <v>34</v>
@@ -10156,22 +10174,22 @@
     </row>
     <row r="190" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="8" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C190" s="9" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="E190" s="9" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="F190" s="9" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G190" s="10" t="s">
         <v>16</v>
@@ -10182,22 +10200,22 @@
     </row>
     <row r="191" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="G191" s="6" t="s">
         <v>16</v>
@@ -10208,22 +10226,22 @@
     </row>
     <row r="192" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C192" s="9" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="F192" s="9" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="G192" s="12" t="s">
         <v>34</v>
@@ -10234,22 +10252,22 @@
     </row>
     <row r="193" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="F193" s="5" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="G193" s="11" t="s">
         <v>34</v>
@@ -10260,22 +10278,22 @@
     </row>
     <row r="194" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="8" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C194" s="9" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="D194" s="9" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="E194" s="9" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="F194" s="9" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="G194" s="12" t="s">
         <v>34</v>
@@ -10286,22 +10304,22 @@
     </row>
     <row r="195" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="G195" s="11" t="s">
         <v>34</v>
@@ -10312,22 +10330,22 @@
     </row>
     <row r="196" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="8" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C196" s="9" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="D196" s="9" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="E196" s="9" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="F196" s="9" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="G196" s="10" t="s">
         <v>16</v>
@@ -10338,22 +10356,22 @@
     </row>
     <row r="197" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="G197" s="6" t="s">
         <v>16</v>
@@ -10364,22 +10382,22 @@
     </row>
     <row r="198" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="8" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C198" s="9" t="s">
         <v>617</v>
       </c>
       <c r="D198" s="9" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="F198" s="9" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="G198" s="10" t="s">
         <v>16</v>
@@ -10390,22 +10408,22 @@
     </row>
     <row r="199" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="G199" s="6" t="s">
         <v>16</v>
@@ -10416,22 +10434,22 @@
     </row>
     <row r="200" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="8" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C200" s="9" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="D200" s="9" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="E200" s="9" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="F200" s="9" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="G200" s="10" t="s">
         <v>16</v>
@@ -10442,22 +10460,22 @@
     </row>
     <row r="201" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="G201" s="6" t="s">
         <v>16</v>
@@ -10468,22 +10486,22 @@
     </row>
     <row r="202" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="8" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C202" s="9" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D202" s="9" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="E202" s="9" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="F202" s="9" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="G202" s="10" t="s">
         <v>16</v>
@@ -10494,22 +10512,22 @@
     </row>
     <row r="203" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="G203" s="11" t="s">
         <v>34</v>
@@ -10520,22 +10538,22 @@
     </row>
     <row r="204" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="8" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C204" s="9" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="D204" s="9" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="E204" s="9" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="F204" s="9" t="s">
-        <v>669</v>
+        <v>904</v>
       </c>
       <c r="G204" s="10" t="s">
         <v>16</v>
@@ -10546,22 +10564,22 @@
     </row>
     <row r="205" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="G205" s="6" t="s">
         <v>16</v>
@@ -10572,22 +10590,22 @@
     </row>
     <row r="206" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="8" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C206" s="9" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="D206" s="9" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="E206" s="9" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="F206" s="9" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="G206" s="10" t="s">
         <v>16</v>
@@ -10598,22 +10616,22 @@
     </row>
     <row r="207" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="G207" s="6" t="s">
         <v>16</v>
@@ -10624,22 +10642,22 @@
     </row>
     <row r="208" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="8" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C208" s="9" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="D208" s="9" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="E208" s="9" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="F208" s="9" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="G208" s="10" t="s">
         <v>16</v>
@@ -10650,22 +10668,22 @@
     </row>
     <row r="209" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="G209" s="6" t="s">
         <v>16</v>
@@ -10676,22 +10694,22 @@
     </row>
     <row r="210" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="8" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C210" s="9" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="D210" s="9" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="E210" s="9" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="F210" s="9" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="G210" s="10" t="s">
         <v>16</v>
@@ -10702,22 +10720,22 @@
     </row>
     <row r="211" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="G211" s="6" t="s">
         <v>16</v>
@@ -10728,22 +10746,22 @@
     </row>
     <row r="212" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="8" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C212" s="9" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="D212" s="9" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="E212" s="9" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="F212" s="9" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="G212" s="10" t="s">
         <v>16</v>
@@ -10754,22 +10772,22 @@
     </row>
     <row r="213" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="G213" s="6" t="s">
         <v>16</v>
@@ -10780,22 +10798,22 @@
     </row>
     <row r="214" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="8" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C214" s="9" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="D214" s="9" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="E214" s="9" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="F214" s="9" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="G214" s="10" t="s">
         <v>16</v>
@@ -10806,22 +10824,22 @@
     </row>
     <row r="215" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="G215" s="6" t="s">
         <v>16</v>
@@ -10832,22 +10850,22 @@
     </row>
     <row r="216" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="8" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C216" s="9" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="D216" s="9" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="E216" s="9" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="F216" s="9" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="G216" s="10" t="s">
         <v>16</v>
@@ -10858,22 +10876,22 @@
     </row>
     <row r="217" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="F217" s="5" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="G217" s="6" t="s">
         <v>16</v>
@@ -10884,22 +10902,22 @@
     </row>
     <row r="218" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="8" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C218" s="9" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="D218" s="9" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E218" s="9" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="F218" s="9" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="G218" s="10" t="s">
         <v>16</v>
@@ -10910,22 +10928,22 @@
     </row>
     <row r="219" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="F219" s="5" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="G219" s="6" t="s">
         <v>16</v>
@@ -10936,22 +10954,22 @@
     </row>
     <row r="220" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="8" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C220" s="9" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="D220" s="9" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="E220" s="9" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="F220" s="9" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="G220" s="10" t="s">
         <v>16</v>
@@ -10962,22 +10980,22 @@
     </row>
     <row r="221" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="F221" s="5" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="G221" s="6" t="s">
         <v>16</v>
@@ -10988,22 +11006,22 @@
     </row>
     <row r="222" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="8" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C222" s="9" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="D222" s="9" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E222" s="9" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="F222" s="9" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="G222" s="10" t="s">
         <v>16</v>
@@ -11014,22 +11032,22 @@
     </row>
     <row r="223" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="F223" s="5" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="G223" s="6" t="s">
         <v>16</v>
@@ -11040,22 +11058,22 @@
     </row>
     <row r="224" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="8" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C224" s="9" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="D224" s="9" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="E224" s="9" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="F224" s="9" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="G224" s="12" t="s">
         <v>34</v>
@@ -11066,22 +11084,22 @@
     </row>
     <row r="225" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="G225" s="6" t="s">
         <v>16</v>
@@ -11092,22 +11110,22 @@
     </row>
     <row r="226" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="8" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="B226" s="9" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C226" s="9" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="D226" s="9" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="E226" s="9" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="F226" s="9" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="G226" s="10" t="s">
         <v>16</v>
@@ -11118,22 +11136,22 @@
     </row>
     <row r="227" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="F227" s="5" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="G227" s="6" t="s">
         <v>16</v>
@@ -11144,22 +11162,22 @@
     </row>
     <row r="228" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="8" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="B228" s="9" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C228" s="9" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="D228" s="9" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="E228" s="9" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="F228" s="9" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="G228" s="10" t="s">
         <v>16</v>
@@ -11170,22 +11188,22 @@
     </row>
     <row r="229" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="F229" s="5" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="G229" s="6" t="s">
         <v>16</v>
@@ -11196,22 +11214,22 @@
     </row>
     <row r="230" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="8" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C230" s="9" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="D230" s="9" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="E230" s="9" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="F230" s="9" t="s">
-        <v>225</v>
+        <v>1018</v>
       </c>
       <c r="G230" s="10" t="s">
         <v>16</v>
@@ -11222,22 +11240,22 @@
     </row>
     <row r="231" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="F231" s="5" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="G231" s="6" t="s">
         <v>16</v>
@@ -11248,22 +11266,22 @@
     </row>
     <row r="232" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="8" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B232" s="9" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C232" s="9" t="s">
         <v>1020</v>
       </c>
-      <c r="B232" s="9" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C232" s="9" t="s">
-        <v>1016</v>
-      </c>
       <c r="D232" s="9" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="E232" s="9" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="F232" s="9" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="G232" s="10" t="s">
         <v>16</v>
@@ -11274,22 +11292,22 @@
     </row>
     <row r="233" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="F233" s="5" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="G233" s="6" t="s">
         <v>16</v>
@@ -11300,22 +11318,22 @@
     </row>
     <row r="234" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="8" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="B234" s="9" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C234" s="9" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="D234" s="9" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="E234" s="9" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="F234" s="9" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="G234" s="10" t="s">
         <v>16</v>
@@ -11326,22 +11344,22 @@
     </row>
     <row r="235" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C235" s="5" t="s">
         <v>1034</v>
       </c>
-      <c r="B235" s="5" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C235" s="5" t="s">
-        <v>1030</v>
-      </c>
       <c r="D235" s="5" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="F235" s="5" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="G235" s="6" t="s">
         <v>16</v>
@@ -11352,22 +11370,22 @@
     </row>
     <row r="236" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="8" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="B236" s="9" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C236" s="9" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="D236" s="9" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="E236" s="9" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="F236" s="9" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="G236" s="10" t="s">
         <v>16</v>
@@ -11378,22 +11396,22 @@
     </row>
     <row r="237" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="F237" s="5" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="G237" s="6" t="s">
         <v>16</v>
@@ -11404,22 +11422,22 @@
     </row>
     <row r="238" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="8" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="B238" s="9" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C238" s="9" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="D238" s="9" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="E238" s="9" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="F238" s="9" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="G238" s="10" t="s">
         <v>16</v>
@@ -11430,22 +11448,22 @@
     </row>
     <row r="239" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="F239" s="5" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="G239" s="6" t="s">
         <v>16</v>
@@ -11456,22 +11474,22 @@
     </row>
     <row r="240" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="8" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B240" s="9" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C240" s="9" t="s">
         <v>1055</v>
       </c>
-      <c r="B240" s="9" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C240" s="9" t="s">
-        <v>1051</v>
-      </c>
       <c r="D240" s="9" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="E240" s="9" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="F240" s="9" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="G240" s="10" t="s">
         <v>16</v>
@@ -11482,22 +11500,22 @@
     </row>
     <row r="241" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="F241" s="5" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="G241" s="6" t="s">
         <v>16</v>
@@ -11508,22 +11526,22 @@
     </row>
     <row r="242" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="8" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="B242" s="9" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C242" s="9" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="D242" s="9" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="E242" s="9" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="F242" s="9" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="G242" s="10" t="s">
         <v>16</v>
@@ -11534,22 +11552,22 @@
     </row>
     <row r="243" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="F243" s="5" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="G243" s="6" t="s">
         <v>16</v>
@@ -11560,22 +11578,22 @@
     </row>
     <row r="244" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="8" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B244" s="9" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C244" s="9" t="s">
         <v>1074</v>
       </c>
-      <c r="B244" s="9" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C244" s="9" t="s">
-        <v>1070</v>
-      </c>
       <c r="D244" s="9" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="E244" s="9" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="F244" s="9" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="G244" s="10" t="s">
         <v>16</v>
@@ -11586,22 +11604,22 @@
     </row>
     <row r="245" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="E245" s="5" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="F245" s="5" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="G245" s="6" t="s">
         <v>16</v>
@@ -11612,22 +11630,22 @@
     </row>
     <row r="246" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="8" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="B246" s="9" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C246" s="9" t="s">
         <v>639</v>
       </c>
       <c r="D246" s="9" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="E246" s="9" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="F246" s="9" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="G246" s="10" t="s">
         <v>16</v>
@@ -11638,22 +11656,22 @@
     </row>
     <row r="247" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="E247" s="5" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="G247" s="6" t="s">
         <v>16</v>
@@ -11664,22 +11682,22 @@
     </row>
     <row r="248" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="8" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B248" s="9" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C248" s="9" t="s">
         <v>1091</v>
       </c>
-      <c r="B248" s="9" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C248" s="9" t="s">
-        <v>1087</v>
-      </c>
       <c r="D248" s="9" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="E248" s="9" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="F248" s="9" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="G248" s="10" t="s">
         <v>16</v>
@@ -11690,22 +11708,22 @@
     </row>
     <row r="249" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="F249" s="5" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="G249" s="6" t="s">
         <v>16</v>
@@ -11716,22 +11734,22 @@
     </row>
     <row r="250" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="8" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="B250" s="9" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C250" s="9" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="D250" s="9" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="E250" s="9" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="F250" s="9" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="G250" s="10" t="s">
         <v>16</v>
@@ -11742,22 +11760,22 @@
     </row>
     <row r="251" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="E251" s="5" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="F251" s="5" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="G251" s="6" t="s">
         <v>16</v>
@@ -11768,22 +11786,22 @@
     </row>
     <row r="252" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="8" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="B252" s="9" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C252" s="9" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="D252" s="9" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="E252" s="9" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="F252" s="9" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="G252" s="10" t="s">
         <v>16</v>
@@ -11794,22 +11812,22 @@
     </row>
     <row r="253" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="E253" s="5" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="F253" s="5" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="G253" s="6" t="s">
         <v>16</v>
@@ -11820,22 +11838,22 @@
     </row>
     <row r="254" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="8" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B254" s="9" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C254" s="9" t="s">
         <v>1119</v>
       </c>
-      <c r="B254" s="9" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C254" s="9" t="s">
-        <v>1115</v>
-      </c>
       <c r="D254" s="9" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="E254" s="9" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="F254" s="9" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="G254" s="10" t="s">
         <v>16</v>
@@ -11846,22 +11864,22 @@
     </row>
     <row r="255" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="E255" s="5" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="F255" s="5" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="G255" s="6" t="s">
         <v>16</v>
@@ -11872,22 +11890,22 @@
     </row>
     <row r="256" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="8" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="B256" s="9" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C256" s="9" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="D256" s="9" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="E256" s="9" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="F256" s="9" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="G256" s="10" t="s">
         <v>16</v>
@@ -11898,22 +11916,22 @@
     </row>
     <row r="257" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="E257" s="5" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="F257" s="5" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="G257" s="6" t="s">
         <v>16</v>
@@ -11924,22 +11942,22 @@
     </row>
     <row r="258" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="8" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B258" s="9" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C258" s="9" t="s">
         <v>1137</v>
       </c>
-      <c r="B258" s="9" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C258" s="9" t="s">
-        <v>1133</v>
-      </c>
       <c r="D258" s="9" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="E258" s="9" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="F258" s="9" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="G258" s="10" t="s">
         <v>16</v>
@@ -11950,22 +11968,22 @@
     </row>
     <row r="259" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="E259" s="5" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="F259" s="5" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="G259" s="11" t="s">
         <v>34</v>
@@ -11976,22 +11994,22 @@
     </row>
     <row r="260" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="8" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="B260" s="9" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C260" s="9" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="D260" s="9" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="E260" s="9" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="F260" s="9" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="G260" s="10" t="s">
         <v>16</v>
@@ -12002,22 +12020,22 @@
     </row>
     <row r="261" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C261" s="5" t="s">
         <v>1151</v>
       </c>
-      <c r="B261" s="5" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C261" s="5" t="s">
-        <v>1147</v>
-      </c>
       <c r="D261" s="5" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="E261" s="5" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="F261" s="5" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="G261" s="6" t="s">
         <v>16</v>
@@ -12028,22 +12046,22 @@
     </row>
     <row r="262" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" s="8" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="B262" s="9" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C262" s="9" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="D262" s="9" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="E262" s="9" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="F262" s="9" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="G262" s="10" t="s">
         <v>16</v>
@@ -12054,22 +12072,22 @@
     </row>
     <row r="263" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="E263" s="5" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="F263" s="5" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="G263" s="6" t="s">
         <v>16</v>
@@ -12080,22 +12098,22 @@
     </row>
     <row r="264" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="8" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="B264" s="9" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C264" s="9" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="D264" s="9" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="E264" s="9" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="F264" s="9" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="G264" s="10" t="s">
         <v>16</v>
@@ -12106,22 +12124,22 @@
     </row>
     <row r="265" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="E265" s="5" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="F265" s="5" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="G265" s="6" t="s">
         <v>16</v>
@@ -12132,22 +12150,22 @@
     </row>
     <row r="266" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="8" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="B266" s="9" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C266" s="9" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D266" s="9" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="E266" s="9" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="F266" s="9" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="G266" s="10" t="s">
         <v>16</v>
@@ -12158,22 +12176,22 @@
     </row>
     <row r="267" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="E267" s="5" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="F267" s="5" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="G267" s="6" t="s">
         <v>16</v>
@@ -12184,22 +12202,22 @@
     </row>
     <row r="268" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" s="8" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B268" s="9" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C268" s="9" t="s">
         <v>1182</v>
       </c>
-      <c r="B268" s="9" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C268" s="9" t="s">
-        <v>1178</v>
-      </c>
       <c r="D268" s="9" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="E268" s="9" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="F268" s="9" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="G268" s="10" t="s">
         <v>16</v>
@@ -12210,22 +12228,22 @@
     </row>
     <row r="269" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="E269" s="5" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="F269" s="5" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="G269" s="6" t="s">
         <v>16</v>
@@ -12236,22 +12254,22 @@
     </row>
     <row r="270" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" s="8" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="B270" s="9" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C270" s="9" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="D270" s="9" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="E270" s="9" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="F270" s="9" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="G270" s="10" t="s">
         <v>16</v>
@@ -12262,22 +12280,22 @@
     </row>
     <row r="271" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" s="4" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C271" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D271" s="5" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
       <c r="E271" s="5" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="F271" s="5" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="G271" s="6" t="s">
         <v>16</v>
@@ -12288,22 +12306,22 @@
     </row>
     <row r="272" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="8" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
       <c r="B272" s="9" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C272" s="9" t="s">
         <v>71</v>
       </c>
       <c r="D272" s="9" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="E272" s="9" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="F272" s="9" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="G272" s="10" t="s">
         <v>16</v>
@@ -12314,22 +12332,22 @@
     </row>
     <row r="273" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" s="4" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C273" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="E273" s="5" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="F273" s="5" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="G273" s="6" t="s">
         <v>16</v>
@@ -12340,22 +12358,22 @@
     </row>
     <row r="274" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" s="8" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="B274" s="9" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C274" s="9" t="s">
         <v>71</v>
       </c>
       <c r="D274" s="9" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="E274" s="9" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="F274" s="9" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="G274" s="10" t="s">
         <v>16</v>
@@ -12366,22 +12384,22 @@
     </row>
     <row r="275" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="E275" s="5" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="F275" s="5" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="G275" s="11" t="s">
         <v>34</v>
@@ -12392,22 +12410,22 @@
     </row>
     <row r="276" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" s="8" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="B276" s="9" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C276" s="9" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="D276" s="9" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="E276" s="9" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="F276" s="9" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="G276" s="10" t="s">
         <v>16</v>
@@ -12418,22 +12436,22 @@
     </row>
     <row r="277" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="D277" s="5" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="E277" s="5" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="F277" s="5" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="G277" s="6" t="s">
         <v>16</v>
@@ -12444,22 +12462,22 @@
     </row>
     <row r="278" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" s="8" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="B278" s="9" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C278" s="9" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="D278" s="9" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="E278" s="9" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="F278" s="9" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="G278" s="10" t="s">
         <v>16</v>
@@ -12470,22 +12488,22 @@
     </row>
     <row r="279" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="D279" s="5" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="E279" s="5" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
       <c r="F279" s="5" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="G279" s="11" t="s">
         <v>34</v>
@@ -12496,22 +12514,22 @@
     </row>
     <row r="280" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" s="8" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="B280" s="9" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C280" s="9" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="D280" s="9" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="E280" s="9" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
       <c r="F280" s="9" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="G280" s="10" t="s">
         <v>16</v>
@@ -12522,22 +12540,22 @@
     </row>
     <row r="281" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="D281" s="5" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="E281" s="5" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="F281" s="5" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="G281" s="11" t="s">
         <v>34</v>
@@ -12548,22 +12566,22 @@
     </row>
     <row r="282" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" s="8" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B282" s="9" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C282" s="9" t="s">
         <v>1244</v>
       </c>
-      <c r="B282" s="9" t="s">
-        <v>1192</v>
-      </c>
-      <c r="C282" s="9" t="s">
-        <v>1240</v>
-      </c>
       <c r="D282" s="9" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="E282" s="9" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="F282" s="9" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="G282" s="10" t="s">
         <v>16</v>
@@ -12574,22 +12592,22 @@
     </row>
     <row r="283" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" s="4" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="E283" s="5" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="F283" s="5" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="G283" s="6" t="s">
         <v>16</v>
@@ -12600,22 +12618,22 @@
     </row>
     <row r="284" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="8" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B284" s="9" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C284" s="9" t="s">
         <v>1253</v>
       </c>
-      <c r="B284" s="9" t="s">
-        <v>1192</v>
-      </c>
-      <c r="C284" s="9" t="s">
-        <v>1249</v>
-      </c>
       <c r="D284" s="9" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E284" s="9" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="F284" s="9" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="G284" s="12" t="s">
         <v>34</v>
@@ -12626,22 +12644,22 @@
     </row>
     <row r="285" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="E285" s="5" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="F285" s="5" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="G285" s="6" t="s">
         <v>16</v>
@@ -12652,22 +12670,22 @@
     </row>
     <row r="286" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" s="8" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="B286" s="9" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C286" s="9" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="D286" s="9" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="E286" s="9" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
       <c r="F286" s="9" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="G286" s="10" t="s">
         <v>16</v>
@@ -12678,22 +12696,22 @@
     </row>
     <row r="287" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" s="4" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="D287" s="5" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="E287" s="5" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="F287" s="5" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="G287" s="11" t="s">
         <v>34</v>
@@ -12704,22 +12722,22 @@
     </row>
     <row r="288" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" s="8" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
       <c r="B288" s="9" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C288" s="9" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="D288" s="9" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="E288" s="9" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="F288" s="9" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="G288" s="12" t="s">
         <v>34</v>
@@ -12730,22 +12748,22 @@
     </row>
     <row r="289" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C289" s="5" t="s">
         <v>1274</v>
       </c>
-      <c r="B289" s="5" t="s">
-        <v>1192</v>
-      </c>
-      <c r="C289" s="5" t="s">
-        <v>1270</v>
-      </c>
       <c r="D289" s="5" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="E289" s="5" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="F289" s="5" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="G289" s="6" t="s">
         <v>16</v>
@@ -12756,22 +12774,22 @@
     </row>
     <row r="290" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" s="8" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="B290" s="9" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C290" s="9" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="D290" s="9" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="E290" s="9" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="F290" s="9" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="G290" s="10" t="s">
         <v>16</v>
@@ -12782,22 +12800,22 @@
     </row>
     <row r="291" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" s="4" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="D291" s="5" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="E291" s="5" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="F291" s="5" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="G291" s="6" t="s">
         <v>16</v>
@@ -12808,22 +12826,22 @@
     </row>
     <row r="292" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" s="8" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="B292" s="9" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C292" s="9" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="D292" s="9" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="E292" s="9" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="F292" s="9" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="G292" s="10" t="s">
         <v>16</v>
@@ -12834,22 +12852,22 @@
     </row>
     <row r="293" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="4" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C293" s="5" t="s">
         <v>1292</v>
       </c>
-      <c r="B293" s="5" t="s">
-        <v>1192</v>
-      </c>
-      <c r="C293" s="5" t="s">
-        <v>1288</v>
-      </c>
       <c r="D293" s="5" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="E293" s="5" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="F293" s="5" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="G293" s="6" t="s">
         <v>16</v>
@@ -12860,22 +12878,22 @@
     </row>
     <row r="294" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" s="8" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="B294" s="9" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C294" s="9" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="D294" s="9" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="E294" s="9" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="F294" s="9" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="G294" s="10" t="s">
         <v>16</v>
@@ -12886,22 +12904,22 @@
     </row>
     <row r="295" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="4" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="E295" s="5" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="F295" s="5" t="s">
-        <v>229</v>
+        <v>1310</v>
       </c>
       <c r="G295" s="6" t="s">
         <v>16</v>
@@ -12912,22 +12930,22 @@
     </row>
     <row r="296" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" s="8" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B296" s="9" t="s">
         <v>1306</v>
       </c>
-      <c r="B296" s="9" t="s">
-        <v>1302</v>
-      </c>
       <c r="C296" s="9" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="D296" s="9" t="s">
-        <v>1308</v>
+        <v>1313</v>
       </c>
       <c r="E296" s="9" t="s">
-        <v>1309</v>
+        <v>1314</v>
       </c>
       <c r="F296" s="9" t="s">
-        <v>1310</v>
+        <v>1315</v>
       </c>
       <c r="G296" s="10" t="s">
         <v>16</v>
@@ -12938,22 +12956,22 @@
     </row>
     <row r="297" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" s="4" t="s">
-        <v>1311</v>
+        <v>1316</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>1312</v>
+        <v>1317</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
       <c r="E297" s="5" t="s">
-        <v>1314</v>
+        <v>1319</v>
       </c>
       <c r="F297" s="5" t="s">
-        <v>1315</v>
+        <v>1320</v>
       </c>
       <c r="G297" s="6" t="s">
         <v>16</v>
@@ -12964,22 +12982,22 @@
     </row>
     <row r="298" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" s="8" t="s">
-        <v>1316</v>
+        <v>1321</v>
       </c>
       <c r="B298" s="9" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C298" s="9" t="s">
-        <v>1312</v>
+        <v>1317</v>
       </c>
       <c r="D298" s="9" t="s">
-        <v>1317</v>
+        <v>1322</v>
       </c>
       <c r="E298" s="9" t="s">
-        <v>1318</v>
+        <v>1323</v>
       </c>
       <c r="F298" s="9" t="s">
-        <v>1319</v>
+        <v>1324</v>
       </c>
       <c r="G298" s="10" t="s">
         <v>16</v>
@@ -12990,22 +13008,22 @@
     </row>
     <row r="299" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" s="4" t="s">
-        <v>1320</v>
+        <v>1325</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>1312</v>
+        <v>1317</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>1321</v>
+        <v>1326</v>
       </c>
       <c r="E299" s="5" t="s">
-        <v>1322</v>
+        <v>1327</v>
       </c>
       <c r="F299" s="5" t="s">
-        <v>1323</v>
+        <v>1328</v>
       </c>
       <c r="G299" s="6" t="s">
         <v>16</v>
@@ -13016,22 +13034,22 @@
     </row>
     <row r="300" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" s="8" t="s">
-        <v>1324</v>
+        <v>1329</v>
       </c>
       <c r="B300" s="9" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C300" s="9" t="s">
-        <v>1312</v>
+        <v>1317</v>
       </c>
       <c r="D300" s="9" t="s">
-        <v>1325</v>
+        <v>1330</v>
       </c>
       <c r="E300" s="9" t="s">
-        <v>1326</v>
+        <v>1331</v>
       </c>
       <c r="F300" s="9" t="s">
-        <v>1327</v>
+        <v>1332</v>
       </c>
       <c r="G300" s="10" t="s">
         <v>16</v>
@@ -13042,22 +13060,22 @@
     </row>
     <row r="301" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" s="4" t="s">
-        <v>1328</v>
+        <v>1333</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>1329</v>
+        <v>1334</v>
       </c>
       <c r="D301" s="5" t="s">
-        <v>1330</v>
+        <v>1335</v>
       </c>
       <c r="E301" s="5" t="s">
-        <v>1331</v>
+        <v>1336</v>
       </c>
       <c r="F301" s="5" t="s">
-        <v>1332</v>
+        <v>1337</v>
       </c>
       <c r="G301" s="6" t="s">
         <v>16</v>
@@ -13068,22 +13086,22 @@
     </row>
     <row r="302" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" s="8" t="s">
-        <v>1333</v>
+        <v>1338</v>
       </c>
       <c r="B302" s="9" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C302" s="9" t="s">
-        <v>1329</v>
+        <v>1334</v>
       </c>
       <c r="D302" s="9" t="s">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="E302" s="9" t="s">
-        <v>1335</v>
+        <v>1340</v>
       </c>
       <c r="F302" s="9" t="s">
-        <v>1336</v>
+        <v>1341</v>
       </c>
       <c r="G302" s="10" t="s">
         <v>16</v>
@@ -13094,22 +13112,22 @@
     </row>
     <row r="303" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" s="4" t="s">
-        <v>1337</v>
+        <v>1342</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>1329</v>
+        <v>1334</v>
       </c>
       <c r="D303" s="5" t="s">
-        <v>1338</v>
+        <v>1343</v>
       </c>
       <c r="E303" s="5" t="s">
-        <v>1339</v>
+        <v>1344</v>
       </c>
       <c r="F303" s="5" t="s">
-        <v>1340</v>
+        <v>1345</v>
       </c>
       <c r="G303" s="6" t="s">
         <v>16</v>
@@ -13120,22 +13138,22 @@
     </row>
     <row r="304" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" s="8" t="s">
-        <v>1341</v>
+        <v>1346</v>
       </c>
       <c r="B304" s="9" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C304" s="9" t="s">
-        <v>1329</v>
+        <v>1334</v>
       </c>
       <c r="D304" s="9" t="s">
-        <v>1342</v>
+        <v>1347</v>
       </c>
       <c r="E304" s="9" t="s">
-        <v>1343</v>
+        <v>1348</v>
       </c>
       <c r="F304" s="9" t="s">
-        <v>1344</v>
+        <v>1349</v>
       </c>
       <c r="G304" s="10" t="s">
         <v>16</v>
@@ -13146,22 +13164,22 @@
     </row>
     <row r="305" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="4" t="s">
-        <v>1345</v>
+        <v>1350</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>1347</v>
+        <v>1352</v>
       </c>
       <c r="D305" s="5" t="s">
-        <v>1348</v>
+        <v>1353</v>
       </c>
       <c r="E305" s="5" t="s">
-        <v>1349</v>
+        <v>1354</v>
       </c>
       <c r="F305" s="5" t="s">
-        <v>233</v>
+        <v>1355</v>
       </c>
       <c r="G305" s="6" t="s">
         <v>16</v>
@@ -13172,22 +13190,22 @@
     </row>
     <row r="306" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" s="8" t="s">
-        <v>1350</v>
+        <v>1356</v>
       </c>
       <c r="B306" s="9" t="s">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="C306" s="9" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="D306" s="9" t="s">
-        <v>1352</v>
+        <v>1358</v>
       </c>
       <c r="E306" s="9" t="s">
-        <v>1353</v>
+        <v>1359</v>
       </c>
       <c r="F306" s="9" t="s">
-        <v>1354</v>
+        <v>1360</v>
       </c>
       <c r="G306" s="10" t="s">
         <v>16</v>
@@ -13198,22 +13216,22 @@
     </row>
     <row r="307" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" s="4" t="s">
-        <v>1355</v>
+        <v>1361</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="D307" s="5" t="s">
-        <v>1356</v>
+        <v>1362</v>
       </c>
       <c r="E307" s="5" t="s">
-        <v>1357</v>
+        <v>1363</v>
       </c>
       <c r="F307" s="5" t="s">
-        <v>1358</v>
+        <v>1364</v>
       </c>
       <c r="G307" s="6" t="s">
         <v>16</v>
@@ -13224,22 +13242,22 @@
     </row>
     <row r="308" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" s="8" t="s">
-        <v>1359</v>
+        <v>1365</v>
       </c>
       <c r="B308" s="9" t="s">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="C308" s="9" t="s">
-        <v>1360</v>
+        <v>1366</v>
       </c>
       <c r="D308" s="9" t="s">
-        <v>1361</v>
+        <v>1367</v>
       </c>
       <c r="E308" s="9" t="s">
-        <v>1362</v>
+        <v>1368</v>
       </c>
       <c r="F308" s="9" t="s">
-        <v>1363</v>
+        <v>1369</v>
       </c>
       <c r="G308" s="10" t="s">
         <v>16</v>
@@ -13250,22 +13268,22 @@
     </row>
     <row r="309" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" s="4" t="s">
-        <v>1364</v>
+        <v>1370</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>1360</v>
+        <v>1366</v>
       </c>
       <c r="D309" s="5" t="s">
-        <v>1365</v>
+        <v>1371</v>
       </c>
       <c r="E309" s="5" t="s">
-        <v>1366</v>
+        <v>1372</v>
       </c>
       <c r="F309" s="5" t="s">
-        <v>1367</v>
+        <v>1373</v>
       </c>
       <c r="G309" s="6" t="s">
         <v>16</v>
@@ -13276,22 +13294,22 @@
     </row>
     <row r="310" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" s="8" t="s">
-        <v>1368</v>
+        <v>1374</v>
       </c>
       <c r="B310" s="9" t="s">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="C310" s="9" t="s">
-        <v>1369</v>
+        <v>1375</v>
       </c>
       <c r="D310" s="9" t="s">
-        <v>1370</v>
+        <v>1376</v>
       </c>
       <c r="E310" s="9" t="s">
-        <v>1371</v>
+        <v>1377</v>
       </c>
       <c r="F310" s="9" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="G310" s="10" t="s">
         <v>16</v>
@@ -13302,22 +13320,22 @@
     </row>
     <row r="311" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" s="4" t="s">
-        <v>1373</v>
+        <v>1379</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>1374</v>
+        <v>1380</v>
       </c>
       <c r="D311" s="5" t="s">
-        <v>1375</v>
+        <v>1381</v>
       </c>
       <c r="E311" s="5" t="s">
-        <v>1376</v>
+        <v>1382</v>
       </c>
       <c r="F311" s="5" t="s">
-        <v>1377</v>
+        <v>1383</v>
       </c>
       <c r="G311" s="6" t="s">
         <v>16</v>
@@ -13328,22 +13346,22 @@
     </row>
     <row r="312" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" s="8" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B312" s="9" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C312" s="9" t="s">
-        <v>1379</v>
+        <v>1385</v>
       </c>
       <c r="D312" s="9" t="s">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="E312" s="9" t="s">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="F312" s="9" t="s">
-        <v>1382</v>
+        <v>1388</v>
       </c>
       <c r="G312" s="10" t="s">
         <v>16</v>
@@ -13354,22 +13372,22 @@
     </row>
     <row r="313" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" s="4" t="s">
-        <v>1383</v>
+        <v>1389</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>1384</v>
+        <v>1390</v>
       </c>
       <c r="D313" s="5" t="s">
-        <v>1385</v>
+        <v>1391</v>
       </c>
       <c r="E313" s="5" t="s">
-        <v>1386</v>
+        <v>1392</v>
       </c>
       <c r="F313" s="5" t="s">
-        <v>1387</v>
+        <v>1393</v>
       </c>
       <c r="G313" s="6" t="s">
         <v>16</v>
@@ -13380,22 +13398,22 @@
     </row>
     <row r="314" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" s="8" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B314" s="9" t="s">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="C314" s="9" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="D314" s="9" t="s">
-        <v>1390</v>
+        <v>1396</v>
       </c>
       <c r="E314" s="9" t="s">
-        <v>1391</v>
+        <v>1397</v>
       </c>
       <c r="F314" s="9" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="G314" s="10" t="s">
         <v>16</v>
@@ -13406,22 +13424,22 @@
     </row>
     <row r="315" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" s="4" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>1395</v>
+        <v>1401</v>
       </c>
       <c r="D315" s="5" t="s">
-        <v>1396</v>
+        <v>1402</v>
       </c>
       <c r="E315" s="5" t="s">
-        <v>1397</v>
+        <v>1403</v>
       </c>
       <c r="F315" s="5" t="s">
-        <v>1398</v>
+        <v>1404</v>
       </c>
       <c r="G315" s="11" t="s">
         <v>34</v>
@@ -13432,22 +13450,22 @@
     </row>
     <row r="316" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" s="8" t="s">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="B316" s="9" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="C316" s="9" t="s">
-        <v>1395</v>
+        <v>1401</v>
       </c>
       <c r="D316" s="9" t="s">
-        <v>1400</v>
+        <v>1406</v>
       </c>
       <c r="E316" s="9" t="s">
-        <v>1401</v>
+        <v>1407</v>
       </c>
       <c r="F316" s="9" t="s">
-        <v>1402</v>
+        <v>1408</v>
       </c>
       <c r="G316" s="12" t="s">
         <v>34</v>
@@ -13458,22 +13476,22 @@
     </row>
     <row r="317" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" s="4" t="s">
-        <v>1403</v>
+        <v>1409</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="D317" s="5" t="s">
-        <v>1405</v>
+        <v>1411</v>
       </c>
       <c r="E317" s="5" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
       <c r="F317" s="5" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="G317" s="11" t="s">
         <v>34</v>
@@ -13484,22 +13502,22 @@
     </row>
     <row r="318" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" s="8" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="B318" s="9" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="C318" s="9" t="s">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="D318" s="9" t="s">
-        <v>1409</v>
+        <v>1415</v>
       </c>
       <c r="E318" s="9" t="s">
-        <v>1410</v>
+        <v>1416</v>
       </c>
       <c r="F318" s="9" t="s">
-        <v>1411</v>
+        <v>1417</v>
       </c>
       <c r="G318" s="12" t="s">
         <v>34</v>
@@ -13510,22 +13528,22 @@
     </row>
     <row r="319" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" s="4" t="s">
-        <v>1412</v>
+        <v>1418</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="D319" s="5" t="s">
-        <v>1414</v>
+        <v>1420</v>
       </c>
       <c r="E319" s="5" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="F319" s="5" t="s">
-        <v>1416</v>
+        <v>1422</v>
       </c>
       <c r="G319" s="11" t="s">
         <v>34</v>
@@ -13536,22 +13554,22 @@
     </row>
     <row r="320" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" s="8" t="s">
-        <v>1417</v>
+        <v>1423</v>
       </c>
       <c r="B320" s="9" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="C320" s="9" t="s">
-        <v>1418</v>
+        <v>1424</v>
       </c>
       <c r="D320" s="9" t="s">
-        <v>1419</v>
+        <v>1425</v>
       </c>
       <c r="E320" s="9" t="s">
-        <v>1420</v>
+        <v>1426</v>
       </c>
       <c r="F320" s="9" t="s">
-        <v>1421</v>
+        <v>1427</v>
       </c>
       <c r="G320" s="12" t="s">
         <v>34</v>
@@ -13562,22 +13580,22 @@
     </row>
     <row r="321" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" s="4" t="s">
-        <v>1422</v>
+        <v>1428</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>1423</v>
+        <v>1429</v>
       </c>
       <c r="D321" s="5" t="s">
-        <v>1424</v>
+        <v>1430</v>
       </c>
       <c r="E321" s="5" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
       <c r="F321" s="5" t="s">
-        <v>1426</v>
+        <v>1432</v>
       </c>
       <c r="G321" s="11" t="s">
         <v>34</v>
@@ -13588,22 +13606,22 @@
     </row>
     <row r="322" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" s="8" t="s">
-        <v>1427</v>
+        <v>1433</v>
       </c>
       <c r="B322" s="9" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="C322" s="9" t="s">
-        <v>1423</v>
+        <v>1429</v>
       </c>
       <c r="D322" s="9" t="s">
-        <v>1428</v>
+        <v>1434</v>
       </c>
       <c r="E322" s="9" t="s">
-        <v>1429</v>
+        <v>1435</v>
       </c>
       <c r="F322" s="9" t="s">
-        <v>1430</v>
+        <v>1436</v>
       </c>
       <c r="G322" s="12" t="s">
         <v>34</v>
@@ -13614,22 +13632,22 @@
     </row>
     <row r="323" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" s="4" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>1432</v>
+        <v>1438</v>
       </c>
       <c r="D323" s="5" t="s">
-        <v>1433</v>
+        <v>1439</v>
       </c>
       <c r="E323" s="5" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="F323" s="5" t="s">
-        <v>1435</v>
+        <v>1441</v>
       </c>
       <c r="G323" s="11" t="s">
         <v>34</v>
@@ -13640,22 +13658,22 @@
     </row>
     <row r="324" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" s="8" t="s">
-        <v>1436</v>
+        <v>1442</v>
       </c>
       <c r="B324" s="9" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="C324" s="9" t="s">
-        <v>1432</v>
+        <v>1438</v>
       </c>
       <c r="D324" s="9" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="E324" s="9" t="s">
-        <v>1438</v>
+        <v>1444</v>
       </c>
       <c r="F324" s="9" t="s">
-        <v>1439</v>
+        <v>1445</v>
       </c>
       <c r="G324" s="12" t="s">
         <v>34</v>
@@ -13666,22 +13684,22 @@
     </row>
     <row r="325" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" s="4" t="s">
-        <v>1440</v>
+        <v>1446</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>1441</v>
+        <v>1447</v>
       </c>
       <c r="D325" s="5" t="s">
-        <v>1442</v>
+        <v>1448</v>
       </c>
       <c r="E325" s="5" t="s">
-        <v>1443</v>
+        <v>1449</v>
       </c>
       <c r="F325" s="5" t="s">
-        <v>1444</v>
+        <v>1450</v>
       </c>
       <c r="G325" s="11" t="s">
         <v>34</v>
@@ -13692,22 +13710,22 @@
     </row>
     <row r="326" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" s="8" t="s">
-        <v>1445</v>
+        <v>1451</v>
       </c>
       <c r="B326" s="9" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="C326" s="9" t="s">
-        <v>1446</v>
+        <v>1452</v>
       </c>
       <c r="D326" s="9" t="s">
-        <v>1447</v>
+        <v>1453</v>
       </c>
       <c r="E326" s="9" t="s">
-        <v>1448</v>
+        <v>1454</v>
       </c>
       <c r="F326" s="9" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="G326" s="12" t="s">
         <v>34</v>
@@ -13718,22 +13736,22 @@
     </row>
     <row r="327" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" s="4" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>1446</v>
+        <v>1452</v>
       </c>
       <c r="D327" s="5" t="s">
-        <v>1451</v>
+        <v>1457</v>
       </c>
       <c r="E327" s="5" t="s">
-        <v>1452</v>
+        <v>1458</v>
       </c>
       <c r="F327" s="5" t="s">
-        <v>1453</v>
+        <v>1459</v>
       </c>
       <c r="G327" s="11" t="s">
         <v>34</v>
@@ -13744,22 +13762,22 @@
     </row>
     <row r="328" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" s="8" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="B328" s="9" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="C328" s="9" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="D328" s="9" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
       <c r="E328" s="9" t="s">
-        <v>1457</v>
+        <v>1463</v>
       </c>
       <c r="F328" s="9" t="s">
-        <v>1458</v>
+        <v>1464</v>
       </c>
       <c r="G328" s="12" t="s">
         <v>34</v>
@@ -13770,22 +13788,22 @@
     </row>
     <row r="329" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" s="4" t="s">
-        <v>1459</v>
+        <v>1465</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="D329" s="5" t="s">
-        <v>1460</v>
+        <v>1466</v>
       </c>
       <c r="E329" s="5" t="s">
-        <v>1461</v>
+        <v>1467</v>
       </c>
       <c r="F329" s="5" t="s">
-        <v>1462</v>
+        <v>1468</v>
       </c>
       <c r="G329" s="11" t="s">
         <v>34</v>
@@ -13814,7 +13832,7 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="13" t="s">
-        <v>1463</v>
+        <v>1469</v>
       </c>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
@@ -13834,7 +13852,7 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
-        <v>1464</v>
+        <v>1470</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -13845,35 +13863,35 @@
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="14" t="s">
-        <v>1465</v>
+        <v>1471</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14" t="s">
-        <v>1466</v>
+        <v>1472</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="14" t="s">
-        <v>1467</v>
+        <v>1473</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>1468</v>
+        <v>1474</v>
       </c>
       <c r="H6" s="14"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="15" t="s">
-        <v>1469</v>
+        <v>1475</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="16" t="s">
-        <v>1469</v>
+        <v>1475</v>
       </c>
       <c r="E7" s="16"/>
       <c r="F7" s="16" t="s">
-        <v>1470</v>
+        <v>1476</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="H7" s="16"/>
     </row>
@@ -13888,7 +13906,7 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="17" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="17"/>
@@ -13899,14 +13917,14 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3" t="s">
-        <v>1474</v>
+        <v>1480</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>1475</v>
+        <v>1481</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -13918,17 +13936,17 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="18" t="s">
-        <v>1476</v>
+        <v>1482</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="19" t="s">
-        <v>1477</v>
+        <v>1483</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>1479</v>
+        <v>1485</v>
       </c>
       <c r="G13" s="21" t="s">
         <v>17</v>
@@ -13937,17 +13955,17 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="22" t="s">
-        <v>1480</v>
+        <v>1486</v>
       </c>
       <c r="C14" s="22"/>
       <c r="D14" s="23" t="s">
-        <v>1481</v>
+        <v>1487</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>1481</v>
+        <v>1487</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>1482</v>
+        <v>1488</v>
       </c>
       <c r="G14" s="21" t="s">
         <v>17</v>
@@ -13956,17 +13974,17 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="18" t="s">
-        <v>1483</v>
+        <v>1489</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="19" t="s">
-        <v>1484</v>
+        <v>1490</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>1485</v>
+        <v>1491</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="G15" s="21" t="s">
         <v>17</v>
@@ -13975,17 +13993,17 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="22" t="s">
-        <v>1487</v>
+        <v>1493</v>
       </c>
       <c r="C16" s="22"/>
       <c r="D16" s="23" t="s">
-        <v>1488</v>
+        <v>1494</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>1489</v>
+        <v>1495</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>1490</v>
+        <v>1496</v>
       </c>
       <c r="G16" s="21" t="s">
         <v>17</v>
@@ -13994,17 +14012,17 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="18" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="C17" s="18"/>
       <c r="D17" s="19" t="s">
-        <v>1488</v>
+        <v>1494</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>1489</v>
+        <v>1495</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>1492</v>
+        <v>1498</v>
       </c>
       <c r="G17" s="21" t="s">
         <v>17</v>
@@ -14013,17 +14031,17 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="22" t="s">
-        <v>1493</v>
+        <v>1499</v>
       </c>
       <c r="C18" s="22"/>
       <c r="D18" s="23" t="s">
-        <v>1488</v>
+        <v>1494</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>1494</v>
+        <v>1500</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>1495</v>
+        <v>1501</v>
       </c>
       <c r="G18" s="21" t="s">
         <v>17</v>
@@ -14032,17 +14050,17 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="18" t="s">
-        <v>1496</v>
+        <v>1502</v>
       </c>
       <c r="C19" s="18"/>
       <c r="D19" s="19" t="s">
-        <v>1488</v>
+        <v>1494</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>1497</v>
+        <v>1503</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>1498</v>
+        <v>1504</v>
       </c>
       <c r="G19" s="21" t="s">
         <v>17</v>
@@ -14051,17 +14069,17 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="22" t="s">
-        <v>1499</v>
+        <v>1505</v>
       </c>
       <c r="C20" s="22"/>
       <c r="D20" s="23" t="s">
-        <v>1488</v>
+        <v>1494</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>1494</v>
+        <v>1500</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>1500</v>
+        <v>1506</v>
       </c>
       <c r="G20" s="21" t="s">
         <v>17</v>
@@ -14070,17 +14088,17 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="s">
-        <v>1501</v>
+        <v>1507</v>
       </c>
       <c r="C21" s="18"/>
       <c r="D21" s="19" t="s">
-        <v>1488</v>
+        <v>1494</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>1502</v>
+        <v>1508</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>1503</v>
+        <v>1509</v>
       </c>
       <c r="G21" s="21" t="s">
         <v>17</v>
@@ -14089,17 +14107,17 @@
     </row>
     <row r="22" ht="20" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="22" t="s">
-        <v>1504</v>
+        <v>1510</v>
       </c>
       <c r="C22" s="22"/>
       <c r="D22" s="23" t="s">
-        <v>1488</v>
+        <v>1494</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>1505</v>
+        <v>1511</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>1506</v>
+        <v>1512</v>
       </c>
       <c r="G22" s="21" t="s">
         <v>17</v>
@@ -14156,7 +14174,7 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="25" t="s">
-        <v>1507</v>
+        <v>1513</v>
       </c>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
@@ -14166,22 +14184,22 @@
     </row>
     <row r="4" ht="25" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>1508</v>
+        <v>1514</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1510</v>
+        <v>1516</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1511</v>
+        <v>1517</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>1468</v>
+        <v>1474</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1512</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -14198,10 +14216,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -14218,10 +14236,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -14238,10 +14256,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -14258,10 +14276,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -14278,10 +14296,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -14298,10 +14316,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -14318,10 +14336,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -14338,15 +14356,15 @@
         <v>0</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="18" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C13" s="19">
         <v>21</v>
@@ -14358,15 +14376,15 @@
         <v>0</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="22" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C14" s="23">
         <v>14</v>
@@ -14378,15 +14396,15 @@
         <v>0</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="18" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C15" s="19">
         <v>25</v>
@@ -14398,15 +14416,15 @@
         <v>0</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="22" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C16" s="23">
         <v>40</v>
@@ -14418,15 +14436,15 @@
         <v>0</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="18" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C17" s="19">
         <v>25</v>
@@ -14438,15 +14456,15 @@
         <v>0</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="22" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C18" s="23">
         <v>12</v>
@@ -14458,15 +14476,15 @@
         <v>0</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="18" t="s">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="C19" s="19">
         <v>8</v>
@@ -14478,15 +14496,15 @@
         <v>0</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="G19" s="21" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="22" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
       <c r="C20" s="23">
         <v>15</v>
@@ -14498,10 +14516,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
     </row>
   </sheetData>
@@ -14526,7 +14544,7 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="25" t="s">
-        <v>1514</v>
+        <v>1520</v>
       </c>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
@@ -14535,33 +14553,33 @@
     </row>
     <row r="4" ht="25" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>1515</v>
+        <v>1521</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1516</v>
+        <v>1522</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1517</v>
+        <v>1523</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1518</v>
+        <v>1524</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>1519</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
-        <v>1520</v>
+        <v>1526</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>1521</v>
+        <v>1527</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>1522</v>
+        <v>1528</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>1523</v>
+        <v>1529</v>
       </c>
       <c r="F5" s="21" t="s">
         <v>17</v>
@@ -14569,16 +14587,16 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="23" t="s">
-        <v>1524</v>
+        <v>1530</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>1525</v>
+        <v>1531</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>1526</v>
+        <v>1532</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>1527</v>
+        <v>1533</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>17</v>
@@ -14586,16 +14604,16 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
-        <v>1528</v>
+        <v>1534</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>1521</v>
+        <v>1527</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>1529</v>
+        <v>1535</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>1530</v>
+        <v>1536</v>
       </c>
       <c r="F7" s="21" t="s">
         <v>17</v>
@@ -14603,16 +14621,16 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="23" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C8" s="22" t="s">
         <v>1531</v>
       </c>
-      <c r="C8" s="22" t="s">
-        <v>1525</v>
-      </c>
       <c r="D8" s="22" t="s">
-        <v>1532</v>
+        <v>1538</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>1533</v>
+        <v>1539</v>
       </c>
       <c r="F8" s="21" t="s">
         <v>17</v>
@@ -14620,16 +14638,16 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
-        <v>1534</v>
+        <v>1540</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>1525</v>
+        <v>1531</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>1535</v>
+        <v>1541</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>1536</v>
+        <v>1542</v>
       </c>
       <c r="F9" s="21" t="s">
         <v>17</v>
@@ -14637,16 +14655,16 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="23" t="s">
-        <v>1537</v>
+        <v>1543</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>1521</v>
+        <v>1527</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>1538</v>
+        <v>1544</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>1539</v>
+        <v>1545</v>
       </c>
       <c r="F10" s="21" t="s">
         <v>17</v>
@@ -14654,16 +14672,16 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>1525</v>
+        <v>1531</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>1541</v>
+        <v>1547</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>1542</v>
+        <v>1548</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>17</v>
@@ -14671,16 +14689,16 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="23" t="s">
-        <v>1543</v>
+        <v>1549</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>1521</v>
+        <v>1527</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>1429</v>
+        <v>1435</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>1544</v>
+        <v>1550</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>17</v>
@@ -14688,16 +14706,16 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
-        <v>1545</v>
+        <v>1551</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>1521</v>
+        <v>1527</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>1546</v>
+        <v>1552</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>1547</v>
+        <v>1553</v>
       </c>
       <c r="F13" s="21" t="s">
         <v>17</v>
@@ -14705,16 +14723,16 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="23" t="s">
-        <v>1548</v>
+        <v>1554</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>1525</v>
+        <v>1531</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>1549</v>
+        <v>1555</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>1550</v>
+        <v>1556</v>
       </c>
       <c r="F14" s="21" t="s">
         <v>17</v>
